--- a/[Sanico_Kabigting _ S12A] MP Test Cases.xlsx
+++ b/[Sanico_Kabigting _ S12A] MP Test Cases.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\progz\Mantis-in-C-Machine-Project\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE0E0854-DCFE-4EB5-8DE6-233D827A3463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="65">
   <si>
     <t>FUNCTION</t>
   </si>
@@ -32,28 +41,393 @@
   </si>
   <si>
     <t>P/F</t>
+  </si>
+  <si>
+    <t>int PlayerInit()</t>
+  </si>
+  <si>
+    <t>Input 4 players, choose 2 old players, add 2 new players</t>
+  </si>
+  <si>
+    <t>Input 3 players, add 3 new players.</t>
+  </si>
+  <si>
+    <t>3; 0; Burger; 0; Cheese; 0; Cheeseburger;</t>
+  </si>
+  <si>
+    <t>4; 1; 2; 0; maikstrr; 0; takashi</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>Input 6 players, Add 1 new player(input existing player first then a new player), choose 5 old players</t>
+  </si>
+  <si>
+    <t>int deckInit()</t>
+  </si>
+  <si>
+    <t>void scoreFlow()</t>
+  </si>
+  <si>
+    <t>Invalid input(less than 3)</t>
+  </si>
+  <si>
+    <t>Invalid input(greater than 6)</t>
+  </si>
+  <si>
+    <t>1;</t>
+  </si>
+  <si>
+    <t>7;</t>
+  </si>
+  <si>
+    <t>Invalid Input! Follow the minimum and maximum range only!</t>
+  </si>
+  <si>
+    <t>Testing least players</t>
+  </si>
+  <si>
+    <t>3;</t>
+  </si>
+  <si>
+    <t>Seed:65</t>
+  </si>
+  <si>
+    <t>idx:12(back colors:GOB)</t>
+  </si>
+  <si>
+    <t>Seed:67</t>
+  </si>
+  <si>
+    <t>Testing default rand seed (3 players)</t>
+  </si>
+  <si>
+    <t>Testing user chosen seed (3 players)</t>
+  </si>
+  <si>
+    <t>idx:12(back colors:BYO)</t>
+  </si>
+  <si>
+    <t>Successful score (Seed:67)</t>
+  </si>
+  <si>
+    <t>Unsuccesful score (Seed:67)</t>
+  </si>
+  <si>
+    <t>P1 =&gt; [ R: 3 | O: 0 | Y: 0 | G: 0 | B: 0 | I: 0 | V: 1 ] // S:0</t>
+  </si>
+  <si>
+    <t>P1 =&gt; [ R: 3 | O: 1 | Y: 0 | G: 0 | B: 0 | I: 0 | V: 1 ] // S:0</t>
+  </si>
+  <si>
+    <t>P2 =&gt; [ R: 1 | O: 1 | Y: 1 | G: 1 | B: 0 | I: 0 | V: 1 ] // S:0</t>
+  </si>
+  <si>
+    <t>P2 =&gt; [ R: 1 | O: 0 | Y: 1 | G: 1 | B: 0 | I: 0 | V: 1 ] // S:4</t>
+  </si>
+  <si>
+    <t>6; 0; Burger; blt; 1; 2; 3; 4; 5;</t>
+  </si>
+  <si>
+    <t>void stealFlow()</t>
+  </si>
+  <si>
+    <t>Successful steal</t>
+  </si>
+  <si>
+    <t>Unsuccessful steal</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">P1 =&gt; [ R: 1 | O: 2 | Y: 0 | G: 0 | B: 0 | </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>I: 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> | V: 1 ] // S:0
+P3 =&gt; [ R: 0 | O: 1 | Y: 2 | G: 0 | B: 0 | </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>I: 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> | V: 0 ] // S:0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">P1 =&gt; [ R: 1 | O: 2 | Y: 0 | G: 0 | B: 0 | </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>I: 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> | V: 1 ] // S:0
+P3 =&gt; [ R: 0 | O: 1 | Y: 2 | G: 0 | B: 0 | </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>I: 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> | V: 0 ] // S:0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">P3 =&gt; [ R: 0 | O: 1 | Y: 2 | G: 0 | B: 0 | I: 0 | V: 0 ] // S:0
+P1 =&gt; [ R: 1 | O: 2 | Y: 0 | G: 0 | </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>B: 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> | I: 0 | V: 1 ] // S:0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">P3 =&gt; [ R: 0 | O: 1 | Y: 2 | G: 0 | B: 0 | I: 0 | V: 0 ] // S:0
+P1 =&gt; [ R: 1 | O: 2 | Y: 0 | G: 0 | </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>B: 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> | I: 0 | V: 1 ] // S:0</t>
+    </r>
+  </si>
+  <si>
+    <t>void runGame()</t>
+  </si>
+  <si>
+    <t>First player to 20 points</t>
+  </si>
+  <si>
+    <t>Draw pile runs out</t>
+  </si>
+  <si>
+    <t>Tiebreaker(tank pile)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">P1 =&gt; [ R: 1 | O: 1 | Y: 0 | G: 0 | B: 0 | I: 0 | V: 1 ] // </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S:22</t>
+    </r>
+  </si>
+  <si>
+    <t>Player 1 (GUSTAVE), wins!</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">P1 =&gt; [ R: 1 | O: 0 | Y: 1 | G: 0 | B: 11 | I: 0 | V: 0 ] // </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S:4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+P2 =&gt; [ R: 2 | O: 1 | Y: 1 | G: 5 | B: 0 | I: 0 | V: 0 ] // S:0
+P3 =&gt; [ R: 5 | O: 8 | Y: 9 | G: 2 | B: 1 | I: 9 | V: 12 ] // S:0</t>
+    </r>
+  </si>
+  <si>
+    <t>P1 =&gt; [ R: 7 | O: 6 | Y: 10 | G: 9 | B: 6 | I: 9 | V: 5 ] // S:2
+P2 =&gt; [ R: 0 | O: 1 | Y: 1 | G: 1 | B: 5 | I: 0 | V: 1 ] // S:2</t>
+  </si>
+  <si>
+    <t>void mainMenu()</t>
+  </si>
+  <si>
+    <t>Enter Settings</t>
+  </si>
+  <si>
+    <t>Enter New Game</t>
+  </si>
+  <si>
+    <t>Enter Top Players</t>
+  </si>
+  <si>
+    <t>Exit</t>
+  </si>
+  <si>
+    <t>2;</t>
+  </si>
+  <si>
+    <t>0;</t>
+  </si>
+  <si>
+    <t>How many players? (Min: 3, Max: 6):</t>
+  </si>
+  <si>
+    <t>Invalid Input</t>
+  </si>
+  <si>
+    <t>5;</t>
+  </si>
+  <si>
+    <t>[MANTIS TOP PLAYERS]</t>
+  </si>
+  <si>
+    <t>[GAME SETTINGS]</t>
+  </si>
+  <si>
+    <t>Invalid Input! Input Again!</t>
+  </si>
+  <si>
+    <t>Thank you for Playing Mantis!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -62,71 +436,107 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="6">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -134,7 +544,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -324,27 +734,30 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="B2:H59"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="3.88"/>
-    <col customWidth="1" min="2" max="2" width="29.0"/>
-    <col customWidth="1" min="3" max="3" width="5.25"/>
-    <col customWidth="1" min="4" max="4" width="62.88"/>
-    <col customWidth="1" min="5" max="5" width="19.13"/>
-    <col customWidth="1" min="6" max="6" width="25.38"/>
-    <col customWidth="1" min="7" max="7" width="23.5"/>
-    <col customWidth="1" min="8" max="8" width="9.25"/>
+    <col min="1" max="1" width="3.85546875" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" customWidth="1"/>
+    <col min="4" max="4" width="62.85546875" customWidth="1"/>
+    <col min="5" max="5" width="29.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.5703125" customWidth="1"/>
+    <col min="7" max="7" width="25" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2">
+    <row r="2" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -367,235 +780,589 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="4"/>
-      <c r="H3" s="5"/>
-    </row>
-    <row r="4">
+    <row r="3" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
-      <c r="H4" s="5"/>
-    </row>
-    <row r="5">
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B5" s="4"/>
-      <c r="H5" s="5"/>
-    </row>
-    <row r="6">
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B6" s="4"/>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7">
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B7" s="4"/>
-      <c r="H7" s="5"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="4"/>
-      <c r="H8" s="5"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="4"/>
-      <c r="H9" s="5"/>
-    </row>
-    <row r="10">
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="6">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>12</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B9" s="8"/>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B10" s="4"/>
-      <c r="H10" s="5"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="4"/>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12">
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B11" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B12" s="4"/>
-      <c r="H12" s="5"/>
-    </row>
-    <row r="13">
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B13" s="4"/>
       <c r="H13" s="5"/>
     </row>
-    <row r="14">
-      <c r="B14" s="4"/>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15">
+    <row r="14" spans="2:8" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="B14" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" ht="76.5" x14ac:dyDescent="0.2">
       <c r="B15" s="4"/>
-      <c r="H15" s="5"/>
-    </row>
-    <row r="16">
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B16" s="4"/>
       <c r="H16" s="5"/>
     </row>
-    <row r="17">
-      <c r="B17" s="4"/>
-      <c r="H17" s="5"/>
-    </row>
-    <row r="18">
+    <row r="17" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B17" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="76.5" x14ac:dyDescent="0.2">
       <c r="B18" s="4"/>
-      <c r="H18" s="5"/>
-    </row>
-    <row r="19">
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="51" x14ac:dyDescent="0.2">
       <c r="B19" s="4"/>
-      <c r="H19" s="5"/>
-    </row>
-    <row r="20">
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" t="s">
+        <v>48</v>
+      </c>
+      <c r="G19" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
+      <c r="D20" s="6"/>
       <c r="H20" s="5"/>
     </row>
-    <row r="21">
-      <c r="B21" s="4"/>
-      <c r="H21" s="5"/>
-    </row>
-    <row r="22">
+    <row r="21" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B21" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B22" s="4"/>
-      <c r="H22" s="5"/>
-    </row>
-    <row r="23">
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" t="s">
+        <v>61</v>
+      </c>
+      <c r="G22" t="s">
+        <v>61</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B23" s="4"/>
-      <c r="H23" s="5"/>
-    </row>
-    <row r="24">
+      <c r="C23">
+        <v>3</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" t="s">
+        <v>62</v>
+      </c>
+      <c r="G23" t="s">
+        <v>62</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B24" s="4"/>
-      <c r="H24" s="5"/>
-    </row>
-    <row r="25">
+      <c r="C24">
+        <v>4</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E24" t="s">
+        <v>57</v>
+      </c>
+      <c r="F24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G24" t="s">
+        <v>64</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B25" s="4"/>
-      <c r="H25" s="5"/>
-    </row>
-    <row r="26">
+      <c r="C25">
+        <v>5</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E25" t="s">
+        <v>60</v>
+      </c>
+      <c r="F25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G25" t="s">
+        <v>63</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B26" s="4"/>
       <c r="H26" s="5"/>
     </row>
-    <row r="27">
+    <row r="27" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B27" s="4"/>
       <c r="H27" s="5"/>
     </row>
-    <row r="28">
+    <row r="28" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B28" s="4"/>
       <c r="H28" s="5"/>
     </row>
-    <row r="29">
+    <row r="29" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B29" s="4"/>
       <c r="H29" s="5"/>
     </row>
-    <row r="30">
+    <row r="30" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B30" s="4"/>
       <c r="H30" s="5"/>
     </row>
-    <row r="31">
+    <row r="31" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B31" s="4"/>
       <c r="H31" s="5"/>
     </row>
-    <row r="32">
+    <row r="32" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B32" s="4"/>
       <c r="H32" s="5"/>
     </row>
-    <row r="33">
+    <row r="33" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B33" s="4"/>
       <c r="H33" s="5"/>
     </row>
-    <row r="34">
+    <row r="34" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B34" s="4"/>
       <c r="H34" s="5"/>
     </row>
-    <row r="35">
+    <row r="35" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B35" s="4"/>
       <c r="H35" s="5"/>
     </row>
-    <row r="36">
+    <row r="36" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B36" s="4"/>
       <c r="H36" s="5"/>
     </row>
-    <row r="37">
+    <row r="37" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B37" s="4"/>
       <c r="H37" s="5"/>
     </row>
-    <row r="38">
+    <row r="38" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B38" s="4"/>
       <c r="H38" s="5"/>
     </row>
-    <row r="39">
+    <row r="39" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B39" s="4"/>
       <c r="H39" s="5"/>
     </row>
-    <row r="40">
+    <row r="40" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B40" s="4"/>
       <c r="H40" s="5"/>
     </row>
-    <row r="41">
+    <row r="41" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B41" s="4"/>
       <c r="H41" s="5"/>
     </row>
-    <row r="42">
+    <row r="42" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B42" s="4"/>
       <c r="H42" s="5"/>
     </row>
-    <row r="43">
+    <row r="43" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B43" s="4"/>
       <c r="H43" s="5"/>
     </row>
-    <row r="44">
+    <row r="44" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B44" s="4"/>
       <c r="H44" s="5"/>
     </row>
-    <row r="45">
+    <row r="45" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B45" s="4"/>
       <c r="H45" s="5"/>
     </row>
-    <row r="46">
+    <row r="46" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B46" s="4"/>
       <c r="H46" s="5"/>
     </row>
-    <row r="47">
+    <row r="47" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B47" s="4"/>
       <c r="H47" s="5"/>
     </row>
-    <row r="48">
+    <row r="48" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B48" s="4"/>
       <c r="H48" s="5"/>
     </row>
-    <row r="49">
+    <row r="49" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B49" s="4"/>
       <c r="H49" s="5"/>
     </row>
-    <row r="50">
+    <row r="50" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B50" s="4"/>
       <c r="H50" s="5"/>
     </row>
-    <row r="51">
+    <row r="51" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B51" s="4"/>
       <c r="H51" s="5"/>
     </row>
-    <row r="52">
+    <row r="52" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B52" s="4"/>
       <c r="H52" s="5"/>
     </row>
-    <row r="53">
+    <row r="53" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B53" s="4"/>
       <c r="H53" s="5"/>
     </row>
-    <row r="54">
+    <row r="54" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B54" s="4"/>
       <c r="H54" s="5"/>
     </row>
-    <row r="55">
+    <row r="55" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B55" s="4"/>
       <c r="H55" s="5"/>
     </row>
-    <row r="56">
+    <row r="56" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B56" s="4"/>
       <c r="H56" s="5"/>
     </row>
-    <row r="57">
+    <row r="57" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B57" s="4"/>
       <c r="H57" s="5"/>
     </row>
-    <row r="58">
+    <row r="58" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B58" s="4"/>
       <c r="H58" s="5"/>
     </row>
-    <row r="59">
+    <row r="59" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B59" s="4"/>
       <c r="H59" s="5"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>